--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260618.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>885,744,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.26%</t>
+          <t>10.27%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>885,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.22%</t>
+          <t>10.24%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>375,416,486</t>
+          <t>374,689,486</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>6.98%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.84%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>184,738,000</t>
+          <t>184,380,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,989,000</t>
+          <t>4,979,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.53%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.50%</t>
         </is>
       </c>
     </row>
@@ -770,29 +770,29 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,036</t>
+          <t>133,920,945</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -814,24 +814,24 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>28,485,000</t>
+          <t>1,966</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,105 +843,105 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>134,180,945</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>144,292,000</t>
+          <t>93,188,442</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,366,000</t>
+          <t>25,824,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>30,366,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>93,188,442</t>
+          <t>144,292,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,44 +953,44 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>129,747,000</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.52%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>25,874,000</t>
+          <t>129,747,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>226,605,516</t>
+          <t>226,166,516</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>344,175,000</t>
+          <t>348,675,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>62,411,000</t>
+          <t>62,290,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>50,567,000</t>
+          <t>269,366,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>269,366,000</t>
+          <t>50,817,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>10,255,552,642</t>
+          <t>9,978,949,617</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,716,618,559</t>
+          <t>11,014,827,791</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-2,351,121,372</t>
+          <t>-2,697,646,041</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
